--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -2243,13 +2243,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2323,13 +2323,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2863,15 +2863,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2883,7 +2879,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2901,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3019,11 +3015,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3513,13 +3513,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3555,13 +3555,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3597,13 +3597,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3639,15 +3639,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3659,7 +3655,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3681,11 +3677,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3719,13 +3719,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3803,15 +3803,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3823,7 +3819,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3841,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3959,15 +3959,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3979,7 +3975,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4001,7 +3997,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -4039,11 +4035,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4411,11 +4411,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4427,7 +4431,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4449,15 +4453,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5369,14 +5369,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -5385,7 +5393,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5453,22 +5461,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5499,14 +5499,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5515,7 +5523,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5537,22 +5545,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5583,20 +5583,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5629,23 +5629,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5679,22 +5679,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5703,7 +5707,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5725,26 +5729,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5775,22 +5775,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5799,7 +5803,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5821,20 +5825,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5867,23 +5871,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5917,26 +5921,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5967,22 +5967,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5991,7 +5999,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6013,20 +6021,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -6105,20 +6113,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -6151,22 +6159,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6175,7 +6191,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6197,30 +6213,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6229,7 +6237,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6251,20 +6259,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6297,27 +6305,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6351,20 +6359,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6397,20 +6405,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6443,20 +6451,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6489,30 +6497,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6543,20 +6543,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7567,11 +7567,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7591,7 +7587,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7629,7 +7625,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7667,7 +7663,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7683,7 +7679,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7701,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7719,7 +7715,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8309,11 +8309,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8323,11 +8327,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8347,15 +8347,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -8365,7 +8361,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8739,15 +8739,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8759,7 +8755,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8777,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8819,13 +8815,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8861,11 +8857,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8941,20 +8941,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -9163,20 +9163,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -9255,20 +9255,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9696,7 +9696,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.094046</t>
+          <t>生成时间: 2026-06-12T14:44:15.862146</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -510,6 +528,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
@@ -532,6 +555,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
@@ -554,6 +582,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
@@ -576,6 +609,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>48.58%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -598,6 +641,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -620,6 +673,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18.61%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -642,6 +705,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12.85%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -664,6 +737,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -686,6 +769,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2015年8月签署的《增资协议》中第五条'业绩承诺和补偿'，各方不再根据被终止条款享有任何权利或承担任何义务，作为补偿，黄学英同意以合计人民币0元的价格向高新同华转让其所持有的赛分有限22万元注册资本。双方将另行签署《股权转让协议》。</t>
         </is>
       </c>
@@ -714,6 +802,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -742,6 +835,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -770,6 +868,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -798,6 +901,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2021年7月10日，赛分有限召开股东会并作出决议，同意黄学英将其持有的公司0.8%的注册资本22.00万元以人民币0元的价格转让给高新同华。本次股权转让系为解决公司与高新同华之间的业绩承诺与补偿事宜。黄学英与高新同华就上述股权转让事宜签署了《股权转让协议》，就该次股权转让事项，黄学英已经取得了免税证明。</t>
         </is>
       </c>
@@ -826,6 +934,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -854,6 +967,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -882,6 +1000,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -910,6 +1033,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -938,6 +1066,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -966,6 +1099,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -994,6 +1132,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -1022,6 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -1050,6 +1198,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -1078,6 +1231,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
         </is>
       </c>
@@ -1100,6 +1258,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>29.20%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1122,6 +1290,16 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10.18%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1144,6 +1322,16 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9.82%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1166,6 +1354,16 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9.36%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1188,6 +1386,16 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9.09%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1210,6 +1418,16 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6.37%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1232,6 +1450,16 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1253,6 +1481,16 @@
         </is>
       </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
@@ -1269,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1519,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1332,6 +1573,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -1364,6 +1620,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -1396,6 +1667,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -1428,6 +1714,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -1460,6 +1761,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -1492,6 +1808,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
@@ -1524,6 +1855,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1556,6 +1902,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1588,6 +1949,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部VC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1620,6 +1996,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1652,6 +2043,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1684,6 +2090,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1716,6 +2137,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
@@ -1747,6 +2183,21 @@
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
@@ -1763,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1937,100 +2388,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2038,20 +2473,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2061,7 +2500,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2083,15 +2522,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2101,15 +2544,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2119,12 +2566,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2137,433 +2584,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2573,35 +2856,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2611,35 +2894,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2651,7 +2934,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2663,17 +2946,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2701,21 +2984,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2739,21 +3026,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2765,7 +3056,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2777,17 +3068,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2803,7 +3094,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2815,17 +3106,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2853,17 +3144,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2879,7 +3170,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2891,17 +3182,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2929,17 +3220,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2955,7 +3246,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2967,17 +3258,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2993,7 +3284,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3005,25 +3296,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3035,7 +3322,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3047,17 +3334,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3073,7 +3360,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3372,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3111,7 +3398,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3410,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3161,17 +3448,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3199,17 +3486,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3225,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3237,21 +3524,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3263,7 +3554,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3275,17 +3566,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3313,17 +3604,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3351,17 +3642,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3377,7 +3668,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3680,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3427,17 +3718,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3453,7 +3744,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3766,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3491,7 +3782,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3503,25 +3794,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3533,7 +3820,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3545,25 +3832,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3587,25 +3870,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3617,7 +3896,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3908,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3667,25 +3946,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3697,7 +3972,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3709,25 +3984,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3739,7 +4010,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3751,25 +4022,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3781,7 +4048,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3793,17 +4060,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3819,7 +4086,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3831,25 +4098,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3861,7 +4124,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3873,21 +4136,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3899,33 +4166,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3937,33 +4208,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3975,33 +4250,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4013,35 +4292,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4062,26 +4341,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4091,31 +4374,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4125,27 +4416,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -4159,27 +4454,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4195,7 +4494,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4506,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4233,7 +4532,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4245,17 +4544,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4283,17 +4582,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4321,21 +4620,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4359,25 +4662,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4387,11 +4686,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4401,25 +4696,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4429,11 +4720,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4443,17 +4730,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4467,11 +4754,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4481,17 +4764,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4507,7 +4790,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4802,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4545,7 +4828,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4557,12 +4840,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4595,12 +4878,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4633,25 +4916,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4661,7 +4940,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4671,21 +4954,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4697,49 +4984,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4747,49 +5022,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4797,49 +5064,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4847,49 +5102,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4897,49 +5140,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4947,99 +5178,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5047,49 +5254,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5097,7 +5292,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5110,34 +5305,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5160,34 +5355,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5210,34 +5405,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5265,29 +5460,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5315,29 +5510,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5357,35 +5552,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5393,7 +5592,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5403,35 +5602,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5439,7 +5642,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5449,27 +5652,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5477,7 +5692,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5487,35 +5702,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5523,7 +5742,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5533,27 +5752,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5561,7 +5792,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5571,35 +5802,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5607,7 +5842,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5617,39 +5852,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5657,7 +5892,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5667,39 +5902,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5707,7 +5942,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5719,30 +5954,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5765,36 +6000,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5803,7 +6034,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5815,32 +6046,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5849,7 +6072,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5861,36 +6084,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5899,7 +6118,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5911,32 +6130,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5945,7 +6156,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5957,40 +6168,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5999,7 +6202,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6011,32 +6214,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6045,7 +6252,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6057,30 +6264,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -6103,32 +6310,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6137,7 +6348,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6149,40 +6360,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6191,7 +6394,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6203,32 +6406,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6237,7 +6444,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6249,30 +6456,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6295,37 +6502,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6359,20 +6562,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6405,20 +6608,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6451,20 +6654,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6497,20 +6700,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6543,20 +6746,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6577,39 +6780,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6617,7 +6824,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6627,39 +6834,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6667,7 +6870,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6677,39 +6880,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6717,7 +6916,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6727,39 +6926,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6767,7 +6962,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6777,39 +6972,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6817,7 +7016,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6827,39 +7026,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6867,7 +7062,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6877,39 +7072,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6917,7 +7108,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6927,7 +7118,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6935,31 +7130,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6967,7 +7162,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6980,29 +7175,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7030,29 +7225,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7080,29 +7275,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7130,29 +7325,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7180,29 +7375,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7230,29 +7425,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7280,29 +7475,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7335,24 +7530,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7385,24 +7580,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7424,30 +7619,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7455,37 +7662,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7493,37 +7712,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7531,71 +7762,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7603,37 +7862,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7641,37 +7912,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7679,37 +7962,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7717,7 +8012,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7739,7 +8034,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7777,7 +8072,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7815,7 +8110,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7831,7 +8126,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7853,7 +8148,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7876,22 +8171,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7905,31 +8200,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7952,22 +8243,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7983,29 +8274,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8021,29 +8312,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8059,29 +8350,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8104,22 +8395,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8142,22 +8433,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8195,7 +8486,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8223,17 +8514,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8249,7 +8540,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8261,17 +8552,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8287,7 +8578,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8299,25 +8590,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8327,7 +8614,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8337,17 +8628,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8363,7 +8654,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8375,17 +8666,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8413,17 +8704,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8439,7 +8730,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8451,17 +8742,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8477,7 +8768,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8780,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8527,21 +8818,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8551,51 +8846,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8603,29 +8882,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8648,22 +8927,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8679,29 +8958,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8717,29 +8996,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8755,29 +9034,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8793,37 +9072,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8842,30 +9117,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8884,34 +9155,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8919,44 +9198,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8965,37 +9236,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -9014,37 +9281,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -9065,32 +9324,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -9099,7 +9354,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9111,23 +9366,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -9153,32 +9408,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -9199,32 +9446,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -9245,32 +9484,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -9279,7 +9514,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9301,22 +9536,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9325,7 +9556,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9566,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9343,31 +9578,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9375,7 +9602,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9612,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9393,7 +9624,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9403,21 +9634,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9425,7 +9648,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9658,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9443,31 +9670,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9475,7 +9694,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9704,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9493,31 +9716,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9525,7 +9740,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9750,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9543,31 +9762,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9575,7 +9786,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9796,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9593,31 +9808,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9625,7 +9832,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9842,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9643,31 +9854,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9675,35 +9874,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 31 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 13 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.862146</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 31 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 13 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:11.049655</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2894,11 +2894,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2918,7 +2914,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2936,7 +2932,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2956,11 +2956,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2994,15 +2998,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3458,15 +3458,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3478,7 +3474,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3496,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3554,7 +3550,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3572,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3592,7 +3588,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3610,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3630,7 +3626,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3652,11 +3648,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4108,13 +4108,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4150,13 +4150,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4192,13 +4192,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4234,13 +4234,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4276,13 +4276,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4356,13 +4356,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4436,15 +4436,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4456,7 +4452,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4478,11 +4474,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4554,15 +4554,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4574,7 +4570,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4596,11 +4592,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4964,15 +4964,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4984,7 +4980,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5048,11 +5044,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5124,11 +5124,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -5138,11 +5142,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5238,15 +5238,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5256,7 +5252,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5964,14 +5964,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5980,7 +5988,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6002,20 +6010,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6048,22 +6056,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6094,22 +6094,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -6118,7 +6110,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6140,20 +6132,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -6186,14 +6178,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6224,22 +6224,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6248,7 +6252,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6270,23 +6274,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6320,26 +6324,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6370,26 +6370,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6398,7 +6394,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6420,22 +6416,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6466,26 +6466,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6494,7 +6490,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6516,22 +6512,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6562,30 +6562,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6594,7 +6586,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6762,22 +6754,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6808,30 +6808,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6840,7 +6832,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6862,20 +6854,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6908,20 +6900,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6954,20 +6946,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7000,20 +6992,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -7046,22 +7038,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7092,20 +7092,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8866,11 +8866,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -8880,11 +8884,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8904,15 +8904,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8922,7 +8918,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9418,11 +9418,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -9434,7 +9438,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9460,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -9494,15 +9498,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9536,20 +9536,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9582,18 +9582,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9602,7 +9606,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9624,20 +9628,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9670,20 +9674,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9716,22 +9720,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9762,20 +9762,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9808,20 +9808,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9854,20 +9854,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -10291,7 +10291,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.719780</t>
+          <t>生成时间: 2026-06-12T16:30:01.155635</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>auto_extract:赛分科技</t>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第45-60行</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州赛分科技股份有限公司</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -533,50 +533,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>（二）
-股份公司的设立情况”。 
-## 第59页
-苏州赛分科技股份有限公司                            首次公开发行股票并在科创板上市招股说明书 
-1-1-58 
-4、2021 年11 月，报告期内第二次增资 
-2021 年10 月28 日，赛分科技召开2021 年第一次临时股东大会，决议同意
-赛分科技增发股份4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高
-瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、
-吴征涛认购。 
-2021 年10 月28 日，上述新增股东与赛分科技签署了《增资协议》。截至
-2021 年11 月，上述新增股东已支付完毕全部增资款。 
-本次增资具体情况如下： 
-序号 
-股东姓名/名称 
-认购股份 
-（股） 
-股份价格
-（元/股） 
-认购金额 
-（万元） 
-出资方式 
-1 
-源峰磐赛 
-1,571,815 
-127.24 
-20,000.</t>
+          <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>auto_extract:赛分科技</t>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第45-60行</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>圣成投资</t>
+          <t>沈建林</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -586,50 +560,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>（二）
-股份公司的设立情况”。 
-## 第59页
-苏州赛分科技股份有限公司                            首次公开发行股票并在科创板上市招股说明书 
-1-1-58 
-4、2021 年11 月，报告期内第二次增资 
-2021 年10 月28 日，赛分科技召开2021 年第一次临时股东大会，决议同意
-赛分科技增发股份4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高
-瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、
-吴征涛认购。 
-2021 年10 月28 日，上述新增股东与赛分科技签署了《增资协议》。截至
-2021 年11 月，上述新增股东已支付完毕全部增资款。 
-本次增资具体情况如下： 
-序号 
-股东姓名/名称 
-认购股份 
-（股） 
-股份价格
-（元/股） 
-认购金额 
-（万元） 
-出资方式 
-1 
-源峰磐赛 
-1,571,815 
-127.24 
-20,000.</t>
+          <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>auto_extract:赛分科技</t>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第45-60行</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>圣成投资</t>
+          <t>潘鼎</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,209 +587,912 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>第一次临时股东大会，决议同意
-赛分科技增发股份4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高
-瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、
-吴征涛认购。 
-2021 年10 月28 日，上述新增股东与赛分科技签署了《增资协议》。截至
-2021 年11 月，上述新增股东已支付完毕全部增资款。 
-本次增资具体情况如下： 
-序号 
-股东姓名/名称 
-认购股份 
-（股） 
-股份价格
-（元/股） 
-认购金额 
-（万元） 
-出资方式 
-1 
-源峰磐赛 
-1,571,815 
-127.24 
-20,000.00 
-货币 
-2 
-珠海峦恒 
-628,726 
-8,000.00 
-货币 
-3 
-高瓴祈睿 
-628,726 
-8,000.00 
-货币 
-4 
-国药中生 
-461,846 
-5,876.59 
-货币 
-5 
-圣成投资 
-9,699 
-123.41 
-货币 
-6 
-国药二期 
-155,625 
-1,980.20 
-货</t>
+          <t>苏州众勤会计师事务所有限公司出具苏众勤（2009）第...号验资报告...赛分有限（筹）股东黄学英、沈建林、潘鼎签署了《苏州赛分科技有限公司章程》。江苏省苏州工商行政管理局出具《名称预先登记核准通知书》。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>auto_extract:赛分科技</t>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>圣祁投资</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>48.58%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>由新增股东源峰磐赛、珠海峦恒、高
-瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、
-吴征涛认购。 
-2021 年10 月28 日，上述新增股东与赛分科技签署了《增资协议》。截至
-2021 年11 月，上述新增股东已支付完毕全部增资款。 
-本次增资具体情况如下： 
-序号 
-股东姓名/名称 
-认购股份 
-（股） 
-股份价格
-（元/股） 
-认购金额 
-（万元） 
-出资方式 
-1 
-源峰磐赛 
-1,571,815 
-127.24 
-20,000.00 
-货币 
-2 
-珠海峦恒 
-628,726 
-8,000.00 
-货币 
-3 
-高瓴祈睿 
-628,726 
-8,000.00 
-货币 
-4 
-国药中生 
-461,846 
-5,876.59 
-货币 
-5 
-圣成投资 
-9,699 
-123.41 
-货币 
-6 
-国药二期 
-155,625 
-1,980.20 
-货币 
-7 
-圣祁投资 
-1,556 
-19.80 
-货币 
-8</t>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>auto_extract:赛分科技</t>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18.61%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12.85%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第57-58页区域</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>安徽高新同华创业投资基金（有限合伙）</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2015年8月签署的《增资协议》中第五条'业绩承诺和补偿'，各方不再根据被终止条款享有任何权利或承担任何义务，作为补偿，黄学英同意以合计人民币0元的价格向高新同华转让其所持有的赛分有限22万元注册资本。双方将另行签署《股权转让协议》。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第55-56页</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上海复星惟盈股权投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1922.8571</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第55-56页</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第55-56页</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="F13" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2021年2月24日，黄学英与复星惟盈、唐斌、张敏签署了《股权转让协议》。具体情况如下：黄学英向复星惟盈转让37.3190万元注册资本，转让单价51.52元/注册资本，转让价格1,922.8571万元；向朱勤华转让19.4081万元注册资本，转让价格1,000.0000万元；向唐斌转让0.8872万元注册资本，转让价格45.7143万元；向张敏转让0.6100万元注册资本，转让价格31.4286万元。注：上述表格中转让单价和转让金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第57-58页</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>安徽高新同华创业投资基金（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2021年7月10日，赛分有限召开股东会并作出决议，同意黄学英将其持有的公司0.8%的注册资本22.00万元以人民币0元的价格转让给高新同华。本次股权转让系为解决公司与高新同华之间的业绩承诺与补偿事宜。黄学英与高新同华就上述股权转让事宜签署了《股权转让协议》，就该次股权转让事项，黄学英已经取得了免税证明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>源峰磐赛（深圳）股权投资中心（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>由新增股东源峰磐赛、珠海峦恒、高
-瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、
-吴征涛认购。 
-2021 年10 月28 日，上述新增股东与赛分科技签署了《增资协议》。截至
-2021 年11 月，上述新增股东已支付完毕全部增资款。 
-本次增资具体情况如下： 
-序号 
-股东姓名/名称 
-认购股份 
-（股） 
-股份价格
-（元/股） 
-认购金额 
-（万元） 
-出资方式 
-1 
-源峰磐赛 
-1,571,815 
-127.24 
-20,000.00 
-货币 
-2 
-珠海峦恒 
-628,726 
-8,000.00 
-货币 
-3 
-高瓴祈睿 
-628,726 
-8,000.00 
-货币 
-4 
-国药中生 
-461,846 
-5,876.59 
-货币 
-5 
-圣成投资 
-9,699 
-123.41 
-货币 
-6 
-国药二期 
-155,625 
-1,980.20 
-货币 
-7 
-圣祁投资 
-1,556 
-19.80 
-货币 
-8</t>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>珠海峦恒投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高瓴祈睿医疗健康私募投资基金（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>国药中生（上海）生物股权投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5876.59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>国药二期（上海）生物医药投资中心（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1980.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>珠海夏尔巴二期股权投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>甘李药业股份有限公司</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>圣成投资管理（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>123.41</v>
+      </c>
+      <c r="F23" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第59-61页</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>圣祁投资管理（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2021年10月28日，上述新增股东与赛分科技签署了《增资协议》。截至2021年11月，上述新增股东已支付完毕全部增资款。本次增资具体情况如下：源峰磐赛认购1,571,815股，股份价格127.24元/股，认购金额20,000.00万元；珠海峦恒认购628,726股，认购金额8,000.00万元；高瓴祈睿认购628,726股，认购金额8,000.00万元；国药中生认购461,846股，认购金额5,876.59万元；圣成投资认购9,699股，认购金额123.41万元；国药二期认购155,625股，认购金额1,980.20万元；圣祁投资认购1,556股，认购金额19.80万元；夏尔巴二期认购392,954股，认购金额5,000.00万元；甘李药业认购235,772股，认购金额3,000.00万元；吴征涛认购157,182股，认购金额2,000.00万元。合计4,243,901股，54,000.00万元。注：上述表格中增资单价和增资金额之间的细微差异，系计算过程四舍五入造成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>29.20%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10.18%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9.82%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9.36%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9.09%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6.37%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
         </is>
       </c>
     </row>
@@ -856,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -941,6 +1592,617 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>股权转让后（收购美国赛分）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>48.58%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权转让后（收购美国赛分）</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>股权转让后（收购美国赛分）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18.61%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>股权转让后（收购美国赛分）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12.85%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 四、公司在其他证券市场的上市/挂牌情况部分</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>股权转让后（收购美国赛分）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2011年10月，赛分有限以170万美元向黄学英/刘鸿雁、陆民、周乃鼎、史建伟、Cheer Rise Consultants Limited收购美国赛分79,399股股份，占美国赛分股份总数的100%。该次股份收购后，赛分有限持有美国赛分100%的股份。具体转让情况如下：黄学英/刘鸿雁转让38,570股（48.5774%），转让价格825,816美元；陆民转让15,584股（19.6275%），转让价格333,667美元；周乃鼎转让14,778股（18.6123%），转让价格316,410美元；史建伟转让10,200股（12.8465%），转让价格218,391美元；Cheer Rise Consultants Limited转让267股（0.3363%），转让价格5,717美元。总计79,399股，1,700,000美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>29.20%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10.18%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9.82%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部VC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9.36%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9.09%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6.37%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>688758_赛分科技_招股书_正式稿_20250106.md 第52-53页</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>其他后（整体变更为股份有限公司）</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2021年9月16日，赛分科技就整体变更为股份有限公司事项办理完毕工商变更登记手续，取得了江苏省市场监督管理局换发的《营业执照》。整体变更为股份有限公司后，赛分科技的股权结构如下：黄学英持股8,031,668股（29.1989%）；周金清持股2,800,000股（10.1793%）；高新同华持股2,700,000股（9.8158%）；陆民持股2,574,000股（9.3577%）；国寿疌泉持股2,500,615股（9.0909%）；华泰大健康一号持股1,751,887股（6.3689%）；苏州贤达持股1,341,500股（4.8770%）；复星惟盈持股1,263,621股（4.5939%）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -952,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1694,15 +2956,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1714,7 +2972,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1736,7 +2994,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1774,11 +3032,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -1790,7 +3052,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1812,7 +3074,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1850,7 +3112,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1892,7 +3154,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1908,7 +3170,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -1930,7 +3192,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1946,7 +3208,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1968,7 +3230,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1984,7 +3246,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2006,7 +3268,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2044,7 +3306,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2060,7 +3322,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2082,7 +3344,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2098,7 +3360,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2120,7 +3382,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2136,7 +3398,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2158,7 +3420,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2196,7 +3458,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2212,7 +3474,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2310,15 +3572,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2352,11 +3610,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2368,7 +3630,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2390,7 +3652,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2406,7 +3668,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2466,7 +3728,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2482,7 +3744,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2542,7 +3804,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2618,7 +3880,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2694,7 +3956,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2710,7 +3972,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2732,7 +3994,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2770,7 +4032,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2786,7 +4048,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2808,7 +4070,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2846,13 +4108,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2888,15 +4150,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2908,7 +4166,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2930,13 +4188,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2972,13 +4230,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3014,11 +4272,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3030,7 +4292,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3052,13 +4314,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3094,13 +4356,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3136,15 +4398,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3156,7 +4414,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3178,11 +4436,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3194,7 +4456,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3216,7 +4478,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3292,11 +4554,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3308,7 +4574,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3330,7 +4596,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3368,15 +4634,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3388,7 +4650,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3410,7 +4672,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3444,7 +4706,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3478,7 +4740,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3512,7 +4774,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3528,7 +4790,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3550,7 +4812,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3588,7 +4850,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3604,7 +4866,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3626,7 +4888,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3664,7 +4926,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3702,11 +4964,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -3718,7 +4984,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3740,15 +5006,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -3760,7 +5022,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3782,13 +5044,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3824,11 +5086,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -3838,11 +5104,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3862,7 +5124,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3900,7 +5162,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3938,15 +5200,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -3956,7 +5214,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3976,7 +5238,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4014,7 +5276,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4037,30 +5299,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4068,37 +5342,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4106,37 +5392,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4144,37 +5442,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4182,37 +5492,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4220,37 +5542,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4258,37 +5592,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4296,37 +5642,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4334,37 +5692,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4372,75 +5742,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4448,37 +5842,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4486,37 +5892,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4524,29 +5942,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4569,29 +5987,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4600,36 +6026,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -4638,36 +6072,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -4683,22 +6125,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4721,42 +6163,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4764,36 +6202,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -4809,29 +6255,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -4840,35 +6294,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -4885,33 +6351,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -4920,35 +6390,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -4958,35 +6440,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -4996,39 +6490,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5045,33 +6547,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5080,42 +6586,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5133,33 +6639,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5168,42 +6678,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5221,37 +6731,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5260,44 +6778,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5306,42 +6832,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -5359,33 +6885,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -5394,42 +6924,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -5447,37 +6977,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -5486,49 +7024,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5536,49 +7070,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5586,49 +7116,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5636,42 +7162,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5693,35 +7219,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5743,35 +7269,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -5793,35 +7319,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -5840,24 +7366,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 5 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 0 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.826711</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 31 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 13 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.698594</t>
         </is>
       </c>
     </row>
